--- a/research/traditional_assets/database/data/japan/japan_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/japan/japan_insurance_prop_cas.xlsx
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.046</v>
+        <v>0.0406</v>
       </c>
       <c r="E2">
-        <v>0.0431</v>
+        <v>-0.02955</v>
       </c>
       <c r="F2">
-        <v>0.207</v>
+        <v>0.0411</v>
       </c>
       <c r="G2">
-        <v>0.09025261873111222</v>
+        <v>0.1366763094074507</v>
       </c>
       <c r="H2">
-        <v>0.09025261873111222</v>
+        <v>0.1366763094074507</v>
       </c>
       <c r="I2">
-        <v>0.09910949260576767</v>
+        <v>0.05305976052593978</v>
       </c>
       <c r="J2">
-        <v>0.08017925767060481</v>
+        <v>0.03647786926388343</v>
       </c>
       <c r="K2">
-        <v>6941.83</v>
+        <v>2900.8</v>
       </c>
       <c r="L2">
-        <v>0.05355759356799365</v>
+        <v>0.02598791805491972</v>
       </c>
       <c r="M2">
-        <v>4009.0333</v>
+        <v>4016.359</v>
       </c>
       <c r="N2">
-        <v>0.05776238949018522</v>
+        <v>0.05428054967658929</v>
       </c>
       <c r="O2">
-        <v>0.5775182192591867</v>
+        <v>1.384569429123</v>
       </c>
       <c r="P2">
-        <v>2714.5933</v>
+        <v>2183.259</v>
       </c>
       <c r="Q2">
-        <v>0.03911202122018972</v>
+        <v>0.02950645064506451</v>
       </c>
       <c r="R2">
-        <v>0.3910486571984621</v>
+        <v>0.7526403061224489</v>
       </c>
       <c r="S2">
-        <v>1294.44</v>
+        <v>1833.1</v>
       </c>
       <c r="T2">
-        <v>0.3228808301492532</v>
+        <v>0.4564084037308417</v>
       </c>
       <c r="U2">
-        <v>40061</v>
+        <v>34300.4</v>
       </c>
       <c r="V2">
-        <v>0.5772012632986386</v>
+        <v>0.4635652754464636</v>
       </c>
       <c r="W2">
-        <v>0.07120376622138037</v>
+        <v>0.03945486476513278</v>
       </c>
       <c r="X2">
-        <v>0.06110286392182586</v>
+        <v>0.09381101470500691</v>
       </c>
       <c r="Y2">
-        <v>0.01010090229955452</v>
+        <v>-0.05435614993987414</v>
       </c>
       <c r="Z2">
-        <v>1.792267269288455</v>
+        <v>1.521596384739787</v>
       </c>
       <c r="AA2">
-        <v>0.1238597563366799</v>
+        <v>0.4657900846704167</v>
       </c>
       <c r="AB2">
-        <v>0.05237939914426235</v>
+        <v>0.08727435182753601</v>
       </c>
       <c r="AC2">
-        <v>0.07218658366944747</v>
+        <v>0.3788474123027856</v>
       </c>
       <c r="AD2">
-        <v>25911.2</v>
+        <v>17215.67</v>
       </c>
       <c r="AE2">
-        <v>1891.062462741246</v>
+        <v>1569.255821790116</v>
       </c>
       <c r="AF2">
-        <v>27802.26246274124</v>
+        <v>18784.92582179012</v>
       </c>
       <c r="AG2">
-        <v>-12258.73753725876</v>
+        <v>-15515.47417820988</v>
       </c>
       <c r="AH2">
-        <v>0.2860083717343086</v>
+        <v>0.2024728042206339</v>
       </c>
       <c r="AI2">
-        <v>0.2422834795112802</v>
+        <v>0.242190119322918</v>
       </c>
       <c r="AJ2">
-        <v>-0.2145128710303429</v>
+        <v>-0.265325526180844</v>
       </c>
       <c r="AK2">
-        <v>-0.1641283130028881</v>
+        <v>-0.3586370793406382</v>
       </c>
       <c r="AL2">
-        <v>356.933</v>
+        <v>268.635</v>
       </c>
       <c r="AM2">
-        <v>356.691</v>
+        <v>268.511</v>
       </c>
       <c r="AN2">
-        <v>1.622127524244706</v>
+        <v>1.965218751212874</v>
       </c>
       <c r="AO2">
-        <v>36.28658599793238</v>
+        <v>22.08438959927039</v>
       </c>
       <c r="AP2">
-        <v>-0.767437848176819</v>
+        <v>-1.771136458178928</v>
       </c>
       <c r="AQ2">
-        <v>36.31120493648564</v>
+        <v>22.09458830364492</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ipet Holdings,Inc. (TSE:7339)</t>
+          <t>ipet Holdings, Inc. (TSE:7339)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.02664410058027079</v>
+        <v>0.02643624474544605</v>
       </c>
       <c r="H3">
-        <v>0.02664410058027079</v>
+        <v>0.02643624474544605</v>
       </c>
       <c r="I3">
-        <v>0.02938060820854888</v>
+        <v>0.01858387310823231</v>
       </c>
       <c r="J3">
-        <v>0.02938060820854888</v>
+        <v>0.01096519715964665</v>
       </c>
       <c r="K3">
-        <v>-6.57</v>
+        <v>1.53</v>
       </c>
       <c r="L3">
-        <v>-0.03176982591876209</v>
+        <v>0.007146193367585241</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -749,7 +749,7 @@
         <v>-0</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -758,73 +758,70 @@
         <v>-0</v>
       </c>
       <c r="R3">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
       <c r="U3">
-        <v>71.40000000000001</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="V3">
-        <v>0.3472762645914397</v>
+        <v>0.2924847664184158</v>
+      </c>
+      <c r="W3">
+        <v>0.034</v>
       </c>
       <c r="X3">
-        <v>0.05401150289476499</v>
-      </c>
-      <c r="Z3">
-        <v>56.34184836397604</v>
-      </c>
-      <c r="AA3">
-        <v>1.655357772527451</v>
+        <v>0.0895677234036783</v>
+      </c>
+      <c r="Y3">
+        <v>-0.0555677234036783</v>
       </c>
       <c r="AB3">
-        <v>0.05342113241662012</v>
-      </c>
-      <c r="AC3">
-        <v>1.601936640110831</v>
+        <v>0.08815448312961781</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>8.27</v>
       </c>
       <c r="AE3">
-        <v>3.670451112360456</v>
+        <v>2.355963837637317</v>
       </c>
       <c r="AF3">
-        <v>3.670451112360456</v>
+        <v>10.62596383763732</v>
       </c>
       <c r="AG3">
-        <v>-67.72954888763955</v>
+        <v>-75.77403616236269</v>
       </c>
       <c r="AH3">
-        <v>0.01753927079934346</v>
+        <v>0.03472242585036002</v>
       </c>
       <c r="AI3">
-        <v>0.07541436392045893</v>
+        <v>0.2259595119480104</v>
       </c>
       <c r="AJ3">
-        <v>-0.4912550030930262</v>
+        <v>-0.3450140176431057</v>
       </c>
       <c r="AK3">
-        <v>2.979801720766717</v>
+        <v>1.92446707393423</v>
       </c>
       <c r="AL3">
-        <v>0.027</v>
+        <v>0.041</v>
       </c>
       <c r="AM3">
-        <v>0.027</v>
+        <v>0.041</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>1.151810584958217</v>
       </c>
       <c r="AO3">
-        <v>146.6666666666667</v>
+        <v>79.26829268292683</v>
       </c>
       <c r="AP3">
-        <v>-8.101620680339661</v>
+        <v>-10.55348693069118</v>
       </c>
       <c r="AQ3">
-        <v>146.6666666666667</v>
+        <v>79.26829268292683</v>
       </c>
     </row>
     <row r="4">
@@ -835,7 +832,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sompo Holdings, Inc. (TSE:8630)</t>
+          <t>Dream Incubator Inc. (TSE:4310)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -844,124 +841,115 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.046</v>
-      </c>
-      <c r="E4">
-        <v>0.0602</v>
-      </c>
-      <c r="F4">
-        <v>0.09759999999999999</v>
+        <v>0.201</v>
       </c>
       <c r="G4">
-        <v>0.08553689488825206</v>
+        <v>0.01191391237509608</v>
       </c>
       <c r="H4">
-        <v>0.08553689488825206</v>
+        <v>0.01191391237509608</v>
       </c>
       <c r="I4">
-        <v>0.09250476886617019</v>
+        <v>0.03077186603974656</v>
       </c>
       <c r="J4">
-        <v>0.06791284913372078</v>
+        <v>0.02512537799944355</v>
       </c>
       <c r="K4">
-        <v>2094.3</v>
+        <v>7.97</v>
       </c>
       <c r="L4">
-        <v>0.05776471010075658</v>
+        <v>0.03063028439661799</v>
       </c>
       <c r="M4">
-        <v>909</v>
+        <v>-0</v>
       </c>
       <c r="N4">
-        <v>0.06715028662608594</v>
+        <v>-0</v>
       </c>
       <c r="O4">
-        <v>0.4340352385045122</v>
+        <v>-0</v>
       </c>
       <c r="P4">
-        <v>561.4</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.04147213521659476</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.2680609272788043</v>
+        <v>-0</v>
       </c>
       <c r="S4">
-        <v>347.6</v>
-      </c>
-      <c r="T4">
-        <v>0.3823982398239824</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>11239.4</v>
+        <v>107</v>
       </c>
       <c r="V4">
-        <v>0.8302848531410674</v>
+        <v>0.6552357624004899</v>
       </c>
       <c r="W4">
-        <v>0.1291836810224651</v>
+        <v>0.09613992762364293</v>
       </c>
       <c r="X4">
-        <v>0.06586890809594118</v>
+        <v>0.09143613965570419</v>
       </c>
       <c r="Y4">
-        <v>0.06331477292652396</v>
+        <v>0.004703787967938744</v>
       </c>
       <c r="Z4">
-        <v>2.967382521754562</v>
+        <v>53.03923497678228</v>
       </c>
       <c r="AA4">
-        <v>0.2015234015219575</v>
+        <v>1.332630827592962</v>
       </c>
       <c r="AB4">
-        <v>0.05147437592773835</v>
+        <v>0.0880933863447954</v>
       </c>
       <c r="AC4">
-        <v>0.1500490255942191</v>
+        <v>1.244537441248167</v>
       </c>
       <c r="AD4">
-        <v>4804.5</v>
+        <v>10.3</v>
       </c>
       <c r="AE4">
-        <v>1456.37425709397</v>
+        <v>3.615802282289732</v>
       </c>
       <c r="AF4">
-        <v>6260.874257093969</v>
+        <v>13.91580228228973</v>
       </c>
       <c r="AG4">
-        <v>-4978.52574290603</v>
+        <v>-93.08419771771027</v>
       </c>
       <c r="AH4">
-        <v>0.316242917010848</v>
+        <v>0.07852461294689193</v>
       </c>
       <c r="AI4">
-        <v>0.2450787808119341</v>
+        <v>0.12568939569086</v>
       </c>
       <c r="AJ4">
-        <v>-0.5817207527299468</v>
+        <v>-1.325687305308887</v>
       </c>
       <c r="AK4">
-        <v>-0.3479789404414059</v>
+        <v>-25.05090170200081</v>
       </c>
       <c r="AL4">
-        <v>123.1</v>
+        <v>0.09</v>
       </c>
       <c r="AM4">
-        <v>123.1</v>
+        <v>-0.034</v>
       </c>
       <c r="AN4">
-        <v>1.110404918184339</v>
+        <v>0.8699324324324325</v>
       </c>
       <c r="AO4">
-        <v>28.21121039805037</v>
+        <v>68.77777777777779</v>
       </c>
       <c r="AP4">
-        <v>-1.150625345036986</v>
+        <v>-7.861841023455259</v>
       </c>
       <c r="AQ4">
-        <v>28.21121039805037</v>
+        <v>-182.0588235294118</v>
       </c>
     </row>
     <row r="5">
@@ -972,7 +960,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MS&amp;AD Insurance Group Holdings, Inc. (TSE:8725)</t>
+          <t>Anicom Holdings, Inc. (TSE:8715)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -981,124 +969,121 @@
         </is>
       </c>
       <c r="D5">
-        <v>-0.0186</v>
+        <v>0.124</v>
       </c>
       <c r="E5">
-        <v>-0.0231</v>
-      </c>
-      <c r="F5">
-        <v>0.254</v>
+        <v>0.08529999999999999</v>
       </c>
       <c r="G5">
-        <v>0.1020270350599788</v>
+        <v>0.09370037056643726</v>
       </c>
       <c r="H5">
-        <v>0.1020270350599788</v>
+        <v>0.09370037056643726</v>
       </c>
       <c r="I5">
-        <v>0.09758947233878761</v>
+        <v>0.06511381683430387</v>
       </c>
       <c r="J5">
-        <v>0.06477599375046447</v>
+        <v>0.04174613105264244</v>
       </c>
       <c r="K5">
-        <v>1547.3</v>
+        <v>14.8</v>
       </c>
       <c r="L5">
-        <v>0.03679098355783291</v>
+        <v>0.03917416622551614</v>
       </c>
       <c r="M5">
-        <v>1121.58</v>
+        <v>1.3804</v>
       </c>
       <c r="N5">
-        <v>0.0657991845355079</v>
+        <v>0.00386342009515813</v>
       </c>
       <c r="O5">
-        <v>0.7248626639953467</v>
+        <v>0.09327027027027027</v>
       </c>
       <c r="P5">
-        <v>807.38</v>
+        <v>1.3804</v>
       </c>
       <c r="Q5">
-        <v>0.0473661670235546</v>
+        <v>0.00386342009515813</v>
       </c>
       <c r="R5">
-        <v>0.521799263232728</v>
+        <v>0.09327027027027027</v>
       </c>
       <c r="S5">
-        <v>314.1999999999999</v>
+        <v>0</v>
       </c>
       <c r="T5">
-        <v>0.2801405160577043</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>19741.9</v>
+        <v>194</v>
       </c>
       <c r="V5">
-        <v>1.158188378164325</v>
+        <v>0.5429610971172684</v>
       </c>
       <c r="W5">
-        <v>0.05971687263127832</v>
+        <v>0.06113176373399422</v>
       </c>
       <c r="X5">
-        <v>0.06490641809375175</v>
+        <v>0.09187706512235258</v>
       </c>
       <c r="Y5">
-        <v>-0.005189545462473431</v>
+        <v>-0.03074530138835836</v>
       </c>
       <c r="Z5">
-        <v>2.447373343202698</v>
+        <v>20.42162162162162</v>
       </c>
       <c r="AA5">
-        <v>0.1585310403843513</v>
+        <v>0.8525236925236928</v>
       </c>
       <c r="AB5">
-        <v>0.0515871365254956</v>
+        <v>0.08755766937586136</v>
       </c>
       <c r="AC5">
-        <v>0.1069439038588557</v>
+        <v>0.7649660231478314</v>
       </c>
       <c r="AD5">
-        <v>7253.6</v>
+        <v>34.6</v>
       </c>
       <c r="AE5">
-        <v>14.84178291889215</v>
+        <v>0</v>
       </c>
       <c r="AF5">
-        <v>7268.441782918892</v>
+        <v>34.6</v>
       </c>
       <c r="AG5">
-        <v>-12473.45821708111</v>
+        <v>-159.4</v>
       </c>
       <c r="AH5">
-        <v>0.2989413172003703</v>
+        <v>0.08828782852768563</v>
       </c>
       <c r="AI5">
-        <v>0.1941453671783227</v>
+        <v>0.1555755395683453</v>
       </c>
       <c r="AJ5">
-        <v>-2.728203023796029</v>
+        <v>-0.8054573016675088</v>
       </c>
       <c r="AK5">
-        <v>-0.704864816501376</v>
+        <v>-5.612676056338027</v>
       </c>
       <c r="AL5">
-        <v>130.9</v>
+        <v>0.104</v>
       </c>
       <c r="AM5">
-        <v>130.9</v>
+        <v>0.104</v>
       </c>
       <c r="AN5">
-        <v>1.473907512994428</v>
+        <v>1.091482649842271</v>
       </c>
       <c r="AO5">
-        <v>31.31168831168831</v>
+        <v>236.5384615384616</v>
       </c>
       <c r="AP5">
-        <v>-2.534565426709211</v>
+        <v>-5.02839116719243</v>
       </c>
       <c r="AQ5">
-        <v>31.31168831168831</v>
+        <v>236.5384615384616</v>
       </c>
     </row>
     <row r="6">
@@ -1109,7 +1094,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Tokio Marine Holdings, Inc. (TSE:8766)</t>
+          <t>MS&amp;AD Insurance Group Holdings, Inc. (TSE:8725)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1118,124 +1103,124 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0298</v>
+        <v>-0.0159</v>
       </c>
       <c r="E6">
-        <v>0.026</v>
+        <v>-0.111</v>
       </c>
       <c r="F6">
-        <v>0.296</v>
+        <v>0.0411</v>
       </c>
       <c r="G6">
-        <v>0.08481334392374901</v>
+        <v>0.1352607110275847</v>
       </c>
       <c r="H6">
-        <v>0.08481334392374901</v>
+        <v>0.1352607110275847</v>
       </c>
       <c r="I6">
-        <v>0.1064298636879581</v>
+        <v>0.05783648724329758</v>
       </c>
       <c r="J6">
-        <v>0.07590665166491718</v>
+        <v>0.03748259929560403</v>
       </c>
       <c r="K6">
-        <v>3305.3</v>
+        <v>721.5</v>
       </c>
       <c r="L6">
-        <v>0.06563343923749007</v>
+        <v>0.01976598606655508</v>
       </c>
       <c r="M6">
-        <v>1975.919</v>
+        <v>879.261</v>
       </c>
       <c r="N6">
-        <v>0.05213602889763135</v>
+        <v>0.05761188064317446</v>
       </c>
       <c r="O6">
-        <v>0.5978032251232869</v>
+        <v>1.218656964656965</v>
       </c>
       <c r="P6">
-        <v>1344.919</v>
+        <v>321.161</v>
       </c>
       <c r="Q6">
-        <v>0.03548664487206888</v>
+        <v>0.02104345490047046</v>
       </c>
       <c r="R6">
-        <v>0.4068977097389042</v>
+        <v>0.4451295911295911</v>
       </c>
       <c r="S6">
-        <v>631</v>
+        <v>558.0999999999999</v>
       </c>
       <c r="T6">
-        <v>0.319345074367927</v>
+        <v>0.6347375807638459</v>
       </c>
       <c r="U6">
-        <v>8646.700000000001</v>
+        <v>18497.9</v>
       </c>
       <c r="V6">
-        <v>0.2281493325734248</v>
+        <v>1.212039209005491</v>
       </c>
       <c r="W6">
-        <v>0.1009816172090053</v>
+        <v>0.02422254526409793</v>
       </c>
       <c r="X6">
-        <v>0.06352590038048161</v>
+        <v>0.1012982126487399</v>
       </c>
       <c r="Y6">
-        <v>0.03745571682852372</v>
+        <v>-0.07707566738464193</v>
       </c>
       <c r="Z6">
-        <v>1.174975714680747</v>
+        <v>2.109151400991886</v>
       </c>
       <c r="AA6">
-        <v>0.0891884722890086</v>
+        <v>0.0790564768171407</v>
       </c>
       <c r="AB6">
-        <v>0.05175920880896934</v>
+        <v>0.08632767535940096</v>
       </c>
       <c r="AC6">
-        <v>0.03742926348003926</v>
+        <v>-0.007271198542260257</v>
       </c>
       <c r="AD6">
-        <v>13788.8</v>
+        <v>5259</v>
       </c>
       <c r="AE6">
-        <v>409.9603233721523</v>
+        <v>8.533794982139174</v>
       </c>
       <c r="AF6">
-        <v>14198.76032337215</v>
+        <v>5267.53379498214</v>
       </c>
       <c r="AG6">
-        <v>5552.06032337215</v>
+        <v>-13230.36620501786</v>
       </c>
       <c r="AH6">
-        <v>0.2725391355309695</v>
+        <v>0.2565857152300602</v>
       </c>
       <c r="AI6">
-        <v>0.276872538082839</v>
+        <v>0.2093902855580537</v>
       </c>
       <c r="AJ6">
-        <v>0.1277764443288497</v>
+        <v>-6.51282175067595</v>
       </c>
       <c r="AK6">
-        <v>0.1302201306423635</v>
+        <v>-1.986949066787258</v>
       </c>
       <c r="AL6">
-        <v>102.7</v>
+        <v>107</v>
       </c>
       <c r="AM6">
-        <v>102.7</v>
+        <v>107</v>
       </c>
       <c r="AN6">
-        <v>2.063913544582316</v>
+        <v>1.862278502528364</v>
       </c>
       <c r="AO6">
-        <v>52.16650438169425</v>
+        <v>19.70373831775701</v>
       </c>
       <c r="AP6">
-        <v>0.8310347892308148</v>
+        <v>-4.685040228975573</v>
       </c>
       <c r="AQ6">
-        <v>52.16650438169425</v>
+        <v>19.70373831775701</v>
       </c>
     </row>
     <row r="7">
@@ -1246,7 +1231,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dream Incubator Inc. (TSE:4310)</t>
+          <t>Sompo Holdings, Inc. (TSE:8630)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1255,118 +1240,124 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.18</v>
+        <v>0.0406</v>
+      </c>
+      <c r="E7">
+        <v>-0.0992</v>
+      </c>
+      <c r="F7">
+        <v>0.121</v>
       </c>
       <c r="G7">
-        <v>-0.01957142857142857</v>
+        <v>0.1188590862422998</v>
       </c>
       <c r="H7">
-        <v>-0.01957142857142857</v>
+        <v>0.1188590862422998</v>
       </c>
       <c r="I7">
-        <v>-0.02311832017419353</v>
+        <v>0.03279804769300382</v>
       </c>
       <c r="J7">
-        <v>-0.02311832017419353</v>
+        <v>0.02387585151487654</v>
       </c>
       <c r="K7">
-        <v>-17.8</v>
+        <v>512</v>
       </c>
       <c r="L7">
-        <v>-0.06357142857142857</v>
+        <v>0.01642710472279261</v>
       </c>
       <c r="M7">
-        <v>1.64</v>
+        <v>1048.822</v>
       </c>
       <c r="N7">
-        <v>0.01230307576894223</v>
+        <v>0.07086108464911392</v>
       </c>
       <c r="O7">
-        <v>-0.09213483146067415</v>
+        <v>2.04848046875</v>
       </c>
       <c r="P7">
-        <v>-0</v>
+        <v>539.6220000000001</v>
       </c>
       <c r="Q7">
-        <v>-0</v>
+        <v>0.03645823621217342</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>1.05394921875</v>
       </c>
       <c r="S7">
-        <v>1.64</v>
+        <v>509.2</v>
       </c>
       <c r="T7">
-        <v>1</v>
+        <v>0.4854970624185991</v>
       </c>
       <c r="U7">
-        <v>93.2</v>
+        <v>9032.5</v>
       </c>
       <c r="V7">
-        <v>0.6991747936984246</v>
+        <v>0.6102586969887374</v>
       </c>
       <c r="W7">
-        <v>-0.1687203791469194</v>
+        <v>0.02669238589265699</v>
       </c>
       <c r="X7">
-        <v>0.0586798274631701</v>
+        <v>0.1007330470619149</v>
       </c>
       <c r="Y7">
-        <v>-0.2274002066100895</v>
+        <v>-0.07404066116925789</v>
       </c>
       <c r="Z7">
-        <v>4.30930675672654</v>
+        <v>2.263742199478439</v>
       </c>
       <c r="AA7">
-        <v>-0.09962393333081966</v>
+        <v>0.05404877262270723</v>
       </c>
       <c r="AB7">
-        <v>0.05299958947955537</v>
+        <v>0.08638851464794545</v>
       </c>
       <c r="AC7">
-        <v>-0.152623522810375</v>
+        <v>-0.03233974202523821</v>
       </c>
       <c r="AD7">
-        <v>19.5</v>
+        <v>3866.3</v>
       </c>
       <c r="AE7">
-        <v>6.215648243870943</v>
+        <v>1021.752247522283</v>
       </c>
       <c r="AF7">
-        <v>25.71564824387094</v>
+        <v>4888.052247522283</v>
       </c>
       <c r="AG7">
-        <v>-67.48435175612906</v>
+        <v>-4144.447752477717</v>
       </c>
       <c r="AH7">
-        <v>0.1617177210410933</v>
+        <v>0.2482611839286988</v>
       </c>
       <c r="AI7">
-        <v>0.1735015738794257</v>
+        <v>0.2769928698308557</v>
       </c>
       <c r="AJ7">
-        <v>-1.025354206131571</v>
+        <v>-0.3889071029263733</v>
       </c>
       <c r="AK7">
-        <v>-1.22663921829999</v>
+        <v>-0.4811096218720068</v>
       </c>
       <c r="AL7">
-        <v>0.134</v>
+        <v>103.4</v>
       </c>
       <c r="AM7">
-        <v>-0.108</v>
+        <v>103.4</v>
       </c>
       <c r="AN7">
-        <v>-21.42857142857142</v>
+        <v>2.153087932282675</v>
       </c>
       <c r="AO7">
-        <v>-71.49253731343283</v>
+        <v>10.37330754352031</v>
       </c>
       <c r="AP7">
-        <v>74.15862830343852</v>
+        <v>-2.307984492107655</v>
       </c>
       <c r="AQ7">
-        <v>88.70370370370372</v>
+        <v>10.37330754352031</v>
       </c>
     </row>
     <row r="8">
@@ -1377,7 +1368,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Anicom Holdings, Inc. (TSE:8715)</t>
+          <t>Tokio Marine Holdings, Inc. (TSE:8766)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1386,124 +1377,124 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.129</v>
+        <v>0.0292</v>
       </c>
       <c r="E8">
-        <v>0.149</v>
+        <v>0.0401</v>
       </c>
       <c r="F8">
-        <v>0.16</v>
+        <v>0.0298</v>
       </c>
       <c r="G8">
-        <v>0.07621348561388096</v>
+        <v>0.1524377652329874</v>
       </c>
       <c r="H8">
-        <v>0.07621348561388096</v>
+        <v>0.1524377652329874</v>
       </c>
       <c r="I8">
-        <v>0.06259609048978695</v>
+        <v>0.063867068471976</v>
       </c>
       <c r="J8">
-        <v>0.04649995293527031</v>
+        <v>0.04478396623821061</v>
       </c>
       <c r="K8">
-        <v>19.3</v>
+        <v>1643</v>
       </c>
       <c r="L8">
-        <v>0.04238963320887327</v>
+        <v>0.03812162259361607</v>
       </c>
       <c r="M8">
-        <v>0.8942999999999999</v>
+        <v>2086.8956</v>
       </c>
       <c r="N8">
-        <v>0.001528456674072808</v>
+        <v>0.0484044654019488</v>
       </c>
       <c r="O8">
-        <v>0.04633678756476683</v>
+        <v>1.270173828362751</v>
       </c>
       <c r="P8">
-        <v>0.8942999999999999</v>
+        <v>1321.0956</v>
       </c>
       <c r="Q8">
-        <v>0.001528456674072808</v>
+        <v>0.0306421299958018</v>
       </c>
       <c r="R8">
-        <v>0.04633678756476683</v>
+        <v>0.8040752282410226</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>765.7999999999997</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>0.3669565454064879</v>
       </c>
       <c r="U8">
-        <v>268.4</v>
+        <v>6382.6</v>
       </c>
       <c r="V8">
-        <v>0.4587250042727739</v>
+        <v>0.1480411099024208</v>
       </c>
       <c r="W8">
-        <v>0.08269065981148244</v>
+        <v>0.04490972953026555</v>
       </c>
       <c r="X8">
-        <v>0.05557724619161804</v>
+        <v>0.09574496428766124</v>
       </c>
       <c r="Y8">
-        <v>0.0271134136198644</v>
+        <v>-0.05083523475739569</v>
       </c>
       <c r="Z8">
-        <v>-35.29457364341091</v>
+        <v>1.019860624007184</v>
       </c>
       <c r="AA8">
-        <v>-1.641196013289039</v>
+        <v>0.04567340375321814</v>
       </c>
       <c r="AB8">
-        <v>0.05307191235676906</v>
+        <v>0.08699103427921065</v>
       </c>
       <c r="AC8">
-        <v>-1.694267925645808</v>
+        <v>-0.04131763052599251</v>
       </c>
       <c r="AD8">
-        <v>44.8</v>
+        <v>8037.2</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>532.9980131657669</v>
       </c>
       <c r="AF8">
-        <v>44.8</v>
+        <v>8570.198013165767</v>
       </c>
       <c r="AG8">
-        <v>-223.6</v>
+        <v>2187.598013165767</v>
       </c>
       <c r="AH8">
-        <v>0.07112240038101286</v>
+        <v>0.1658194978053441</v>
       </c>
       <c r="AI8">
-        <v>0.1561519693272918</v>
+        <v>0.2492844076782637</v>
       </c>
       <c r="AJ8">
-        <v>-0.6185338865836789</v>
+        <v>0.04828996318229099</v>
       </c>
       <c r="AK8">
-        <v>-12.08648648648647</v>
+        <v>0.07813799419976028</v>
       </c>
       <c r="AL8">
-        <v>0.07199999999999999</v>
+        <v>58</v>
       </c>
       <c r="AM8">
-        <v>0.07199999999999999</v>
+        <v>58</v>
       </c>
       <c r="AN8">
-        <v>1.207547169811321</v>
+        <v>1.965181671475378</v>
       </c>
       <c r="AO8">
-        <v>395.8333333333334</v>
+        <v>46.85689655172413</v>
       </c>
       <c r="AP8">
-        <v>-6.026954177897573</v>
+        <v>0.5348911959425319</v>
       </c>
       <c r="AQ8">
-        <v>395.8333333333334</v>
+        <v>46.85689655172413</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/japan/japan_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/japan/japan_insurance_prop_cas.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ8"/>
+  <dimension ref="A1:AQ9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0406</v>
+        <v>0.0474</v>
       </c>
       <c r="E2">
-        <v>-0.02955</v>
+        <v>0.136</v>
       </c>
       <c r="F2">
-        <v>0.0411</v>
+        <v>0.0298</v>
       </c>
       <c r="G2">
-        <v>0.1366763094074507</v>
+        <v>0.1157021211801773</v>
       </c>
       <c r="H2">
-        <v>0.1366763094074507</v>
+        <v>0.1157021211801773</v>
       </c>
       <c r="I2">
-        <v>0.05305976052593978</v>
+        <v>0.1104597987534985</v>
       </c>
       <c r="J2">
-        <v>0.03647786926388343</v>
+        <v>0.07328347862053174</v>
       </c>
       <c r="K2">
-        <v>2900.8</v>
+        <v>6922.22</v>
       </c>
       <c r="L2">
-        <v>0.02598791805491972</v>
+        <v>0.05791305453626688</v>
       </c>
       <c r="M2">
-        <v>4016.359</v>
+        <v>3610.3714</v>
       </c>
       <c r="N2">
-        <v>0.05428054967658929</v>
+        <v>0.04149198804326215</v>
       </c>
       <c r="O2">
-        <v>1.384569429123</v>
+        <v>0.5215626489767733</v>
       </c>
       <c r="P2">
-        <v>2183.259</v>
+        <v>2504.0114</v>
       </c>
       <c r="Q2">
-        <v>0.02950645064506451</v>
+        <v>0.02877720864645452</v>
       </c>
       <c r="R2">
-        <v>0.7526403061224489</v>
+        <v>0.3617353103484142</v>
       </c>
       <c r="S2">
-        <v>1833.1</v>
+        <v>1106.36</v>
       </c>
       <c r="T2">
-        <v>0.4564084037308417</v>
+        <v>0.306439387371615</v>
       </c>
       <c r="U2">
-        <v>34300.4</v>
+        <v>34205.4</v>
       </c>
       <c r="V2">
-        <v>0.4635652754464636</v>
+        <v>0.3931036147181421</v>
       </c>
       <c r="W2">
-        <v>0.03945486476513278</v>
+        <v>0.1299928603372117</v>
       </c>
       <c r="X2">
-        <v>0.09381101470500691</v>
+        <v>0.08161898367987701</v>
       </c>
       <c r="Y2">
-        <v>-0.05435614993987414</v>
+        <v>0.04837387665733474</v>
       </c>
       <c r="Z2">
-        <v>1.521596384739787</v>
+        <v>2.831408870598361</v>
       </c>
       <c r="AA2">
-        <v>0.4657900846704167</v>
+        <v>0.4385775946848363</v>
       </c>
       <c r="AB2">
-        <v>0.08727435182753601</v>
+        <v>0.07460186704559006</v>
       </c>
       <c r="AC2">
-        <v>0.3788474123027856</v>
+        <v>0.365145151223875</v>
       </c>
       <c r="AD2">
-        <v>17215.67</v>
+        <v>13454.85</v>
       </c>
       <c r="AE2">
-        <v>1569.255821790116</v>
+        <v>1212.541332757933</v>
       </c>
       <c r="AF2">
-        <v>18784.92582179012</v>
+        <v>14667.39133275793</v>
       </c>
       <c r="AG2">
-        <v>-15515.47417820988</v>
+        <v>-19538.00866724207</v>
       </c>
       <c r="AH2">
-        <v>0.2024728042206339</v>
+        <v>0.1442489566202427</v>
       </c>
       <c r="AI2">
-        <v>0.242190119322918</v>
+        <v>0.1739324889203326</v>
       </c>
       <c r="AJ2">
-        <v>-0.265325526180844</v>
+        <v>-0.2895562576882678</v>
       </c>
       <c r="AK2">
-        <v>-0.3586370793406382</v>
+        <v>-0.389803818266823</v>
       </c>
       <c r="AL2">
-        <v>268.635</v>
+        <v>270.664</v>
       </c>
       <c r="AM2">
-        <v>268.511</v>
+        <v>270.524</v>
       </c>
       <c r="AN2">
-        <v>1.965218751212874</v>
+        <v>0.836042969173065</v>
       </c>
       <c r="AO2">
-        <v>22.08438959927039</v>
+        <v>48.87103567522833</v>
       </c>
       <c r="AP2">
-        <v>-1.771136458178928</v>
+        <v>-1.214031726692615</v>
       </c>
       <c r="AQ2">
-        <v>22.09458830364492</v>
+        <v>48.89632712809215</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>ipet Holdings, Inc. (TSE:7339)</t>
+          <t>Zenhoren Co.,Ltd. (TSE:5845)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -725,22 +725,22 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.02643624474544605</v>
+        <v>0</v>
       </c>
       <c r="H3">
-        <v>0.02643624474544605</v>
+        <v>0</v>
       </c>
       <c r="I3">
-        <v>0.01858387310823231</v>
+        <v>0.07971014492753624</v>
       </c>
       <c r="J3">
-        <v>0.01096519715964665</v>
+        <v>0.03985507246376812</v>
       </c>
       <c r="K3">
-        <v>1.53</v>
+        <v>5.81</v>
       </c>
       <c r="L3">
-        <v>0.007146193367585241</v>
+        <v>0.03238573021181716</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -764,64 +764,52 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>86.40000000000001</v>
+        <v>36</v>
       </c>
       <c r="V3">
-        <v>0.2924847664184158</v>
-      </c>
-      <c r="W3">
-        <v>0.034</v>
+        <v>0.2411252511721366</v>
       </c>
       <c r="X3">
-        <v>0.0895677234036783</v>
-      </c>
-      <c r="Y3">
-        <v>-0.0555677234036783</v>
+        <v>0.08161898367987701</v>
       </c>
       <c r="AB3">
-        <v>0.08815448312961781</v>
+        <v>0.07460186704559006</v>
       </c>
       <c r="AD3">
-        <v>8.27</v>
+        <v>32.6</v>
       </c>
       <c r="AE3">
-        <v>2.355963837637317</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>10.62596383763732</v>
+        <v>32.6</v>
       </c>
       <c r="AG3">
-        <v>-75.77403616236269</v>
+        <v>-3.399999999999999</v>
       </c>
       <c r="AH3">
-        <v>0.03472242585036002</v>
+        <v>0.1792193512919186</v>
       </c>
       <c r="AI3">
-        <v>0.2259595119480104</v>
+        <v>0.6185958254269449</v>
       </c>
       <c r="AJ3">
-        <v>-0.3450140176431057</v>
+        <v>-0.02330363262508566</v>
       </c>
       <c r="AK3">
-        <v>1.92446707393423</v>
+        <v>-0.2035928143712574</v>
       </c>
       <c r="AL3">
-        <v>0.041</v>
+        <v>0.737</v>
       </c>
       <c r="AM3">
-        <v>0.041</v>
-      </c>
-      <c r="AN3">
-        <v>1.151810584958217</v>
+        <v>0.737</v>
       </c>
       <c r="AO3">
-        <v>79.26829268292683</v>
-      </c>
-      <c r="AP3">
-        <v>-10.55348693069118</v>
+        <v>19.40298507462687</v>
       </c>
       <c r="AQ3">
-        <v>79.26829268292683</v>
+        <v>19.40298507462687</v>
       </c>
     </row>
     <row r="4">
@@ -832,7 +820,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Dream Incubator Inc. (TSE:4310)</t>
+          <t>Nippon Insure Co., Ltd. (TSE:5843)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -840,26 +828,23 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D4">
-        <v>0.201</v>
-      </c>
       <c r="G4">
-        <v>0.01191391237509608</v>
+        <v>0.1150259067357513</v>
       </c>
       <c r="H4">
-        <v>0.01191391237509608</v>
+        <v>0.1150259067357513</v>
       </c>
       <c r="I4">
-        <v>0.03077186603974656</v>
+        <v>0.1120183121720721</v>
       </c>
       <c r="J4">
-        <v>0.02512537799944355</v>
+        <v>0.0754831088174886</v>
       </c>
       <c r="K4">
-        <v>7.97</v>
+        <v>1.31</v>
       </c>
       <c r="L4">
-        <v>0.03063028439661799</v>
+        <v>0.06787564766839378</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -883,73 +868,67 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>107</v>
+        <v>11.6</v>
       </c>
       <c r="V4">
-        <v>0.6552357624004899</v>
-      </c>
-      <c r="W4">
-        <v>0.09613992762364293</v>
+        <v>0.6783625730994152</v>
       </c>
       <c r="X4">
-        <v>0.09143613965570419</v>
-      </c>
-      <c r="Y4">
-        <v>0.004703787967938744</v>
+        <v>0.08181724422654778</v>
       </c>
       <c r="Z4">
-        <v>53.03923497678228</v>
+        <v>37.45878984372316</v>
       </c>
       <c r="AA4">
-        <v>1.332630827592962</v>
+        <v>2.827505909945192</v>
       </c>
       <c r="AB4">
-        <v>0.0880933863447954</v>
+        <v>0.07456214547046576</v>
       </c>
       <c r="AC4">
-        <v>1.244537441248167</v>
+        <v>2.752943764474726</v>
       </c>
       <c r="AD4">
-        <v>10.3</v>
+        <v>3.35</v>
       </c>
       <c r="AE4">
-        <v>3.615802282289732</v>
+        <v>0.5152328753950399</v>
       </c>
       <c r="AF4">
-        <v>13.91580228228973</v>
+        <v>3.86523287539504</v>
       </c>
       <c r="AG4">
-        <v>-93.08419771771027</v>
+        <v>-7.73476712460496</v>
       </c>
       <c r="AH4">
-        <v>0.07852461294689193</v>
+        <v>0.1843639371128239</v>
       </c>
       <c r="AI4">
-        <v>0.12568939569086</v>
+        <v>0.3437219058266284</v>
       </c>
       <c r="AJ4">
-        <v>-1.325687305308887</v>
+        <v>-0.8259022736024271</v>
       </c>
       <c r="AK4">
-        <v>-25.05090170200081</v>
+        <v>21.80237848480964</v>
       </c>
       <c r="AL4">
-        <v>0.09</v>
+        <v>0.007</v>
       </c>
       <c r="AM4">
-        <v>-0.034</v>
+        <v>-0.005999999999999999</v>
       </c>
       <c r="AN4">
-        <v>0.8699324324324325</v>
+        <v>1.321499013806706</v>
       </c>
       <c r="AO4">
-        <v>68.77777777777779</v>
+        <v>278.5714285714286</v>
       </c>
       <c r="AP4">
-        <v>-7.861841023455259</v>
+        <v>-3.051190187220891</v>
       </c>
       <c r="AQ4">
-        <v>-182.0588235294118</v>
+        <v>-325.0000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -969,121 +948,121 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.124</v>
+        <v>0.114</v>
       </c>
       <c r="E5">
-        <v>0.08529999999999999</v>
+        <v>0.0898</v>
       </c>
       <c r="G5">
-        <v>0.09370037056643726</v>
+        <v>0.09246926229508198</v>
       </c>
       <c r="H5">
-        <v>0.09370037056643726</v>
+        <v>0.09246926229508198</v>
       </c>
       <c r="I5">
-        <v>0.06511381683430387</v>
+        <v>0.07658811475409837</v>
       </c>
       <c r="J5">
-        <v>0.04174613105264244</v>
+        <v>0.04960511347062599</v>
       </c>
       <c r="K5">
-        <v>14.8</v>
+        <v>18.2</v>
       </c>
       <c r="L5">
-        <v>0.03917416622551614</v>
+        <v>0.0466188524590164</v>
       </c>
       <c r="M5">
-        <v>1.3804</v>
+        <v>8.911899999999999</v>
       </c>
       <c r="N5">
-        <v>0.00386342009515813</v>
+        <v>0.02903844900619094</v>
       </c>
       <c r="O5">
-        <v>0.09327027027027027</v>
+        <v>0.4896648351648352</v>
       </c>
       <c r="P5">
-        <v>1.3804</v>
+        <v>2.1519</v>
       </c>
       <c r="Q5">
-        <v>0.00386342009515813</v>
+        <v>0.007011730205278593</v>
       </c>
       <c r="R5">
-        <v>0.09327027027027027</v>
+        <v>0.1182362637362637</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>6.76</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>0.7585363390522785</v>
       </c>
       <c r="U5">
-        <v>194</v>
+        <v>147.1</v>
       </c>
       <c r="V5">
-        <v>0.5429610971172684</v>
+        <v>0.4793092212447052</v>
       </c>
       <c r="W5">
-        <v>0.06113176373399422</v>
+        <v>0.09691160809371671</v>
       </c>
       <c r="X5">
-        <v>0.09187706512235258</v>
+        <v>0.07880178762691505</v>
       </c>
       <c r="Y5">
-        <v>-0.03074530138835836</v>
+        <v>0.01810982046680167</v>
       </c>
       <c r="Z5">
-        <v>20.42162162162162</v>
+        <v>13.74647887323943</v>
       </c>
       <c r="AA5">
-        <v>0.8525236925236928</v>
+        <v>0.6818956443286048</v>
       </c>
       <c r="AB5">
-        <v>0.08755766937586136</v>
+        <v>0.07464669419493113</v>
       </c>
       <c r="AC5">
-        <v>0.7649660231478314</v>
+        <v>0.6072489501336737</v>
       </c>
       <c r="AD5">
-        <v>34.6</v>
+        <v>33.5</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>34.6</v>
+        <v>33.5</v>
       </c>
       <c r="AG5">
-        <v>-159.4</v>
+        <v>-113.6</v>
       </c>
       <c r="AH5">
-        <v>0.08828782852768563</v>
+        <v>0.09841363102232668</v>
       </c>
       <c r="AI5">
-        <v>0.1555755395683453</v>
+        <v>0.1502242152466368</v>
       </c>
       <c r="AJ5">
-        <v>-0.8054573016675088</v>
+        <v>-0.587687532333161</v>
       </c>
       <c r="AK5">
-        <v>-5.612676056338027</v>
+        <v>-1.496706192358366</v>
       </c>
       <c r="AL5">
-        <v>0.104</v>
+        <v>0.1</v>
       </c>
       <c r="AM5">
-        <v>0.104</v>
+        <v>0.1</v>
       </c>
       <c r="AN5">
-        <v>1.091482649842271</v>
+        <v>0.9203296703296704</v>
       </c>
       <c r="AO5">
-        <v>236.5384615384616</v>
+        <v>298.9999999999999</v>
       </c>
       <c r="AP5">
-        <v>-5.02839116719243</v>
+        <v>-3.120879120879121</v>
       </c>
       <c r="AQ5">
-        <v>236.5384615384616</v>
+        <v>298.9999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -1103,124 +1082,124 @@
         </is>
       </c>
       <c r="D6">
-        <v>-0.0159</v>
+        <v>0.0338</v>
       </c>
       <c r="E6">
-        <v>-0.111</v>
+        <v>0.178</v>
       </c>
       <c r="F6">
-        <v>0.0411</v>
+        <v>0.0371</v>
       </c>
       <c r="G6">
-        <v>0.1352607110275847</v>
+        <v>0.09557699094224208</v>
       </c>
       <c r="H6">
-        <v>0.1352607110275847</v>
+        <v>0.09557699094224208</v>
       </c>
       <c r="I6">
-        <v>0.05783648724329758</v>
+        <v>0.09167493867847949</v>
       </c>
       <c r="J6">
-        <v>0.03748259929560403</v>
+        <v>0.06825165310170268</v>
       </c>
       <c r="K6">
-        <v>721.5</v>
+        <v>1892.2</v>
       </c>
       <c r="L6">
-        <v>0.01976598606655508</v>
+        <v>0.0463719954515155</v>
       </c>
       <c r="M6">
-        <v>879.261</v>
+        <v>570.3855000000001</v>
       </c>
       <c r="N6">
-        <v>0.05761188064317446</v>
+        <v>0.02743306287544669</v>
       </c>
       <c r="O6">
-        <v>1.218656964656965</v>
+        <v>0.3014403868512843</v>
       </c>
       <c r="P6">
-        <v>321.161</v>
+        <v>424.3855</v>
       </c>
       <c r="Q6">
-        <v>0.02104345490047046</v>
+        <v>0.02041109759088876</v>
       </c>
       <c r="R6">
-        <v>0.4451295911295911</v>
+        <v>0.224281524151781</v>
       </c>
       <c r="S6">
-        <v>558.0999999999999</v>
+        <v>146.0000000000001</v>
       </c>
       <c r="T6">
-        <v>0.6347375807638459</v>
+        <v>0.2559672361937673</v>
       </c>
       <c r="U6">
-        <v>18497.9</v>
+        <v>19301.5</v>
       </c>
       <c r="V6">
-        <v>1.212039209005491</v>
+        <v>0.9283182393143483</v>
       </c>
       <c r="W6">
-        <v>0.02422254526409793</v>
+        <v>0.09667152016757351</v>
       </c>
       <c r="X6">
-        <v>0.1012982126487399</v>
+        <v>0.08194570003595095</v>
       </c>
       <c r="Y6">
-        <v>-0.07707566738464193</v>
+        <v>0.01472582013162256</v>
       </c>
       <c r="Z6">
-        <v>2.109151400991886</v>
+        <v>6.425889700155775</v>
       </c>
       <c r="AA6">
-        <v>0.0790564768171407</v>
+        <v>0.4385775946848363</v>
       </c>
       <c r="AB6">
-        <v>0.08632767535940096</v>
+        <v>0.07343244346096124</v>
       </c>
       <c r="AC6">
-        <v>-0.007271198542260257</v>
+        <v>0.365145151223875</v>
       </c>
       <c r="AD6">
-        <v>5259</v>
+        <v>4787.8</v>
       </c>
       <c r="AE6">
-        <v>8.533794982139174</v>
+        <v>15.4623110618961</v>
       </c>
       <c r="AF6">
-        <v>5267.53379498214</v>
+        <v>4803.262311061896</v>
       </c>
       <c r="AG6">
-        <v>-13230.36620501786</v>
+        <v>-14498.2376889381</v>
       </c>
       <c r="AH6">
-        <v>0.2565857152300602</v>
+        <v>0.1876628971009099</v>
       </c>
       <c r="AI6">
-        <v>0.2093902855580537</v>
+        <v>0.1651010567370528</v>
       </c>
       <c r="AJ6">
-        <v>-6.51282175067595</v>
+        <v>-2.303624975788047</v>
       </c>
       <c r="AK6">
-        <v>-1.986949066787258</v>
+        <v>-1.480717108441444</v>
       </c>
       <c r="AL6">
-        <v>107</v>
+        <v>69.5</v>
       </c>
       <c r="AM6">
-        <v>107</v>
+        <v>69.5</v>
       </c>
       <c r="AN6">
-        <v>1.862278502528364</v>
+        <v>1.06554914349683</v>
       </c>
       <c r="AO6">
-        <v>19.70373831775701</v>
+        <v>53.7611510791367</v>
       </c>
       <c r="AP6">
-        <v>-4.685040228975573</v>
+        <v>-3.226656241209209</v>
       </c>
       <c r="AQ6">
-        <v>19.70373831775701</v>
+        <v>53.7611510791367</v>
       </c>
     </row>
     <row r="7">
@@ -1240,124 +1219,124 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0406</v>
+        <v>0.0474</v>
       </c>
       <c r="E7">
-        <v>-0.0992</v>
+        <v>0.08689999999999999</v>
       </c>
       <c r="F7">
-        <v>0.121</v>
+        <v>-0.0721</v>
       </c>
       <c r="G7">
-        <v>0.1188590862422998</v>
+        <v>0.07708080872504623</v>
       </c>
       <c r="H7">
-        <v>0.1188590862422998</v>
+        <v>0.07708080872504623</v>
       </c>
       <c r="I7">
-        <v>0.03279804769300382</v>
+        <v>0.09306624722458179</v>
       </c>
       <c r="J7">
-        <v>0.02387585151487654</v>
+        <v>0.06972315067565296</v>
       </c>
       <c r="K7">
-        <v>512</v>
+        <v>1625</v>
       </c>
       <c r="L7">
-        <v>0.01642710472279261</v>
+        <v>0.05182090694559602</v>
       </c>
       <c r="M7">
-        <v>1048.822</v>
+        <v>886.604</v>
       </c>
       <c r="N7">
-        <v>0.07086108464911392</v>
+        <v>0.05505591882610829</v>
       </c>
       <c r="O7">
-        <v>2.04848046875</v>
+        <v>0.5456024615384616</v>
       </c>
       <c r="P7">
-        <v>539.6220000000001</v>
+        <v>615.604</v>
       </c>
       <c r="Q7">
-        <v>0.03645823621217342</v>
+        <v>0.03822748809279855</v>
       </c>
       <c r="R7">
-        <v>1.05394921875</v>
+        <v>0.3788332307692308</v>
       </c>
       <c r="S7">
-        <v>509.2</v>
+        <v>271</v>
       </c>
       <c r="T7">
-        <v>0.4854970624185991</v>
+        <v>0.3056607008314873</v>
       </c>
       <c r="U7">
-        <v>9032.5</v>
+        <v>9007.6</v>
       </c>
       <c r="V7">
-        <v>0.6102586969887374</v>
+        <v>0.5593497146618479</v>
       </c>
       <c r="W7">
-        <v>0.02669238589265699</v>
+        <v>0.1283286476924535</v>
       </c>
       <c r="X7">
-        <v>0.1007330470619149</v>
+        <v>0.08492609463640097</v>
       </c>
       <c r="Y7">
-        <v>-0.07404066116925789</v>
+        <v>0.04340255305605253</v>
       </c>
       <c r="Z7">
-        <v>2.263742199478439</v>
+        <v>3.691894096567046</v>
       </c>
       <c r="AA7">
-        <v>0.05404877262270723</v>
+        <v>0.2574104883734978</v>
       </c>
       <c r="AB7">
-        <v>0.08638851464794545</v>
+        <v>0.0724842744183892</v>
       </c>
       <c r="AC7">
-        <v>-0.03233974202523821</v>
+        <v>0.1849262139551086</v>
       </c>
       <c r="AD7">
-        <v>3866.3</v>
+        <v>4583.4</v>
       </c>
       <c r="AE7">
-        <v>1021.752247522283</v>
+        <v>997.1430976578213</v>
       </c>
       <c r="AF7">
-        <v>4888.052247522283</v>
+        <v>5580.543097657821</v>
       </c>
       <c r="AG7">
-        <v>-4144.447752477717</v>
+        <v>-3427.056902342179</v>
       </c>
       <c r="AH7">
-        <v>0.2482611839286988</v>
+        <v>0.2573547562866325</v>
       </c>
       <c r="AI7">
-        <v>0.2769928698308557</v>
+        <v>0.2572847524579231</v>
       </c>
       <c r="AJ7">
-        <v>-0.3889071029263733</v>
+        <v>-0.2703441972721764</v>
       </c>
       <c r="AK7">
-        <v>-0.4811096218720068</v>
+        <v>-0.2702184314260347</v>
       </c>
       <c r="AL7">
-        <v>103.4</v>
+        <v>106.9</v>
       </c>
       <c r="AM7">
-        <v>103.4</v>
+        <v>106.9</v>
       </c>
       <c r="AN7">
-        <v>2.153087932282675</v>
+        <v>1.240533737515901</v>
       </c>
       <c r="AO7">
-        <v>10.37330754352031</v>
+        <v>27.81478016838166</v>
       </c>
       <c r="AP7">
-        <v>-2.307984492107655</v>
+        <v>-0.927560262630844</v>
       </c>
       <c r="AQ7">
-        <v>10.37330754352031</v>
+        <v>27.81478016838166</v>
       </c>
     </row>
     <row r="8">
@@ -1377,124 +1356,249 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0292</v>
+        <v>0.051</v>
       </c>
       <c r="E8">
-        <v>0.0401</v>
+        <v>0.136</v>
       </c>
       <c r="F8">
         <v>0.0298</v>
       </c>
       <c r="G8">
-        <v>0.1524377652329874</v>
+        <v>0.1598585394692874</v>
       </c>
       <c r="H8">
-        <v>0.1524377652329874</v>
+        <v>0.1598585394692874</v>
       </c>
       <c r="I8">
-        <v>0.063867068471976</v>
+        <v>0.1392039523097185</v>
       </c>
       <c r="J8">
-        <v>0.04478396623821061</v>
+        <v>0.09624212713788254</v>
       </c>
       <c r="K8">
-        <v>1643</v>
+        <v>3313.7</v>
       </c>
       <c r="L8">
-        <v>0.03812162259361607</v>
+        <v>0.07098088440678256</v>
       </c>
       <c r="M8">
-        <v>2086.8956</v>
+        <v>2131.47</v>
       </c>
       <c r="N8">
-        <v>0.0484044654019488</v>
+        <v>0.04309918107370336</v>
       </c>
       <c r="O8">
-        <v>1.270173828362751</v>
+        <v>0.6432296224763859</v>
       </c>
       <c r="P8">
-        <v>1321.0956</v>
+        <v>1461.87</v>
       </c>
       <c r="Q8">
-        <v>0.0306421299958018</v>
+        <v>0.02955959963603275</v>
       </c>
       <c r="R8">
-        <v>0.8040752282410226</v>
+        <v>0.4411594290370281</v>
       </c>
       <c r="S8">
-        <v>765.7999999999997</v>
+        <v>669.5999999999999</v>
       </c>
       <c r="T8">
-        <v>0.3669565454064879</v>
+        <v>0.3141493898577038</v>
       </c>
       <c r="U8">
-        <v>6382.6</v>
+        <v>5655.3</v>
       </c>
       <c r="V8">
-        <v>0.1480411099024208</v>
+        <v>0.1143524416135881</v>
       </c>
       <c r="W8">
-        <v>0.04490972953026555</v>
+        <v>0.1299928603372117</v>
       </c>
       <c r="X8">
-        <v>0.09574496428766124</v>
+        <v>0.07818210215538773</v>
       </c>
       <c r="Y8">
-        <v>-0.05083523475739569</v>
+        <v>0.05181075818182401</v>
       </c>
       <c r="Z8">
-        <v>1.019860624007184</v>
+        <v>1.707409797514385</v>
       </c>
       <c r="AA8">
-        <v>0.04567340375321814</v>
+        <v>0.1643247508088457</v>
       </c>
       <c r="AB8">
-        <v>0.08699103427921065</v>
+        <v>0.07491820587252024</v>
       </c>
       <c r="AC8">
-        <v>-0.04131763052599251</v>
+        <v>0.08940654493632547</v>
       </c>
       <c r="AD8">
-        <v>8037.2</v>
+        <v>4014.2</v>
       </c>
       <c r="AE8">
-        <v>532.9980131657669</v>
+        <v>196.2350439609</v>
       </c>
       <c r="AF8">
-        <v>8570.198013165767</v>
+        <v>4210.4350439609</v>
       </c>
       <c r="AG8">
-        <v>2187.598013165767</v>
+        <v>-1444.8649560391</v>
       </c>
       <c r="AH8">
-        <v>0.1658194978053441</v>
+        <v>0.07845711192896983</v>
       </c>
       <c r="AI8">
-        <v>0.2492844076782637</v>
+        <v>0.1270632260848965</v>
       </c>
       <c r="AJ8">
-        <v>0.04828996318229099</v>
+        <v>-0.03009499878965342</v>
       </c>
       <c r="AK8">
-        <v>0.07813799419976028</v>
+        <v>-0.05257642000906414</v>
       </c>
       <c r="AL8">
-        <v>58</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="AM8">
-        <v>58</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="AN8">
-        <v>1.965181671475378</v>
+        <v>0.5103164210981299</v>
       </c>
       <c r="AO8">
-        <v>46.85689655172413</v>
+        <v>69.31049250535332</v>
       </c>
       <c r="AP8">
-        <v>0.5348911959425319</v>
+        <v>-0.1836825054396843</v>
       </c>
       <c r="AQ8">
-        <v>46.85689655172413</v>
+        <v>69.31049250535332</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dream Incubator Inc. (TSE:4310)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>-0.08039999999999999</v>
+      </c>
+      <c r="E9">
+        <v>0.52</v>
+      </c>
+      <c r="G9">
+        <v>0.1234972677595629</v>
+      </c>
+      <c r="H9">
+        <v>0.1234972677595629</v>
+      </c>
+      <c r="I9">
+        <v>-0.01253693377469069</v>
+      </c>
+      <c r="J9">
+        <v>-0.007992295281365313</v>
+      </c>
+      <c r="K9">
+        <v>66</v>
+      </c>
+      <c r="L9">
+        <v>0.7213114754098361</v>
+      </c>
+      <c r="M9">
+        <v>13</v>
+      </c>
+      <c r="N9">
+        <v>0.0684931506849315</v>
+      </c>
+      <c r="O9">
+        <v>0.196969696969697</v>
+      </c>
+      <c r="P9">
+        <v>-0</v>
+      </c>
+      <c r="Q9">
+        <v>-0</v>
+      </c>
+      <c r="R9">
+        <v>-0</v>
+      </c>
+      <c r="S9">
+        <v>13</v>
+      </c>
+      <c r="T9">
+        <v>1</v>
+      </c>
+      <c r="U9">
+        <v>46.3</v>
+      </c>
+      <c r="V9">
+        <v>0.2439409905163329</v>
+      </c>
+      <c r="W9">
+        <v>0.859375</v>
+      </c>
+      <c r="X9">
+        <v>0.07641865051621369</v>
+      </c>
+      <c r="Y9">
+        <v>0.7829563494837863</v>
+      </c>
+      <c r="AB9">
+        <v>0.07582760780449163</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>3.18564720192099</v>
+      </c>
+      <c r="AF9">
+        <v>3.18564720192099</v>
+      </c>
+      <c r="AG9">
+        <v>-43.114352798079</v>
+      </c>
+      <c r="AH9">
+        <v>0.01650717163742154</v>
+      </c>
+      <c r="AI9">
+        <v>0.02620084915640157</v>
+      </c>
+      <c r="AJ9">
+        <v>-0.2939234589102619</v>
+      </c>
+      <c r="AK9">
+        <v>-0.5726769231649628</v>
+      </c>
+      <c r="AL9">
+        <v>0.02</v>
+      </c>
+      <c r="AM9">
+        <v>-0.107</v>
+      </c>
+      <c r="AN9">
+        <v>0</v>
+      </c>
+      <c r="AO9">
+        <v>-96</v>
+      </c>
+      <c r="AP9">
+        <v>-88.71266007835189</v>
+      </c>
+      <c r="AQ9">
+        <v>17.94392523364486</v>
       </c>
     </row>
   </sheetData>
